--- a/MULTIPUNTO/Datos Multipunto PICARILLO INMUEBLES.xlsx
+++ b/MULTIPUNTO/Datos Multipunto PICARILLO INMUEBLES.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,7 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,8 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -502,10 +521,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7424</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7424</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,13 +530,13 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>46568</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46199</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -562,10 +579,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7424</t>
-        </is>
+      <c r="A3" t="n">
+        <v>7424</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -573,13 +588,13 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>46568</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46199</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,10 +637,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7424</t>
-        </is>
+      <c r="A4" t="n">
+        <v>7424</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -633,13 +646,13 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>46568</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46199</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -676,66 +689,6 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
-        <is>
-          <t>2.0TD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7424</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IBERDROLA</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46568</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>2.0TD</t>
         </is>

--- a/MULTIPUNTO/Datos Multipunto PICARILLO INMUEBLES.xlsx
+++ b/MULTIPUNTO/Datos Multipunto PICARILLO INMUEBLES.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +424,7 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -529,15 +529,11 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46568</v>
-      </c>
+      <c r="C2" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>No</t>
@@ -587,15 +583,11 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46568</v>
-      </c>
+      <c r="C3" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>No</t>
@@ -645,15 +637,11 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46568</v>
-      </c>
+      <c r="C4" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>No</t>
